--- a/ASOS, AWS 지점정보(부산관할)_수정.xlsx
+++ b/ASOS, AWS 지점정보(부산관할)_수정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38C3D409-074D-4F36-A64D-0D3E372831EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92E9A9-294F-4378-9978-458543CFD7D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="3" xr2:uid="{9D2C116D-9A81-45CD-ABAE-F1BEFBD84F46}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{9D2C116D-9A81-45CD-ABAE-F1BEFBD84F46}"/>
   </bookViews>
   <sheets>
     <sheet name="ASOS" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="319">
   <si>
     <t>지점번호</t>
   </si>
@@ -4528,14 +4528,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>대전청 관할</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>청주청 관할</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>옥천</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -4556,10 +4548,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>대구청 관할</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>공성</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -4712,10 +4700,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>전주청 관할</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>무주</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -4756,10 +4740,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>광주청 관할</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>성삼재</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -4830,6 +4810,241 @@
   <si>
     <t>곡성</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 무주군 설천면 심곡리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 구례군 산동면 좌사리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 무주군 설천면 삼공리</t>
+  </si>
+  <si>
+    <t>경상북도 칠곡군 동명면 득명리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 광양시 옥룡면 동곡리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 남원시 산내면 부운리</t>
+  </si>
+  <si>
+    <t>경상북도 경주시 장항리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 구례군 토지면 내동리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 장수군 장수읍 선창리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 진안군 진안읍 반월리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 진안군 동향면 대량리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 장수군 번암면 노단리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 진안군 주천면 신양리</t>
+  </si>
+  <si>
+    <t>충청북도 영동군 추풍령면 관리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 무주군 무주읍 당산리</t>
+  </si>
+  <si>
+    <t>경상북도 김천시 대덕면 중산리</t>
+  </si>
+  <si>
+    <t>경상북도 경주시 산내면 외칠리</t>
+  </si>
+  <si>
+    <t>충청남도 금산군 금산읍 아인리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 순천시 승주읍 평중리</t>
+  </si>
+  <si>
+    <t>대전광역시 중구 사정동</t>
+  </si>
+  <si>
+    <t>충청북도 영동군 양강면 가동리</t>
+  </si>
+  <si>
+    <t>경상북도 영천시 화북면 오산리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 고흥군 동일면 덕흥리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 남원시 도통동</t>
+  </si>
+  <si>
+    <t>경상북도 영천시 신녕면 화성리</t>
+  </si>
+  <si>
+    <t>충청북도 옥천군 청산면 예곡리</t>
+  </si>
+  <si>
+    <t>충청북도 영동군 양산면 원당리</t>
+  </si>
+  <si>
+    <t>충청북도 옥천군 옥천읍 매화리</t>
+  </si>
+  <si>
+    <t>경상북도 칠곡군 가산면 학상리</t>
+  </si>
+  <si>
+    <t>대구광역시 군위군 수서리</t>
+  </si>
+  <si>
+    <t>경상북도 청도군 금천면 신지리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 곡성군 곡성읍 학정리</t>
+  </si>
+  <si>
+    <t>대전광역시 대덕구 장동</t>
+  </si>
+  <si>
+    <t>경상북도 영천시 망정동</t>
+  </si>
+  <si>
+    <t>경상북도 상주시 공성면 장동리</t>
+  </si>
+  <si>
+    <t>대전광역시 동구 세천동</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 광양시 중동</t>
+  </si>
+  <si>
+    <t>대구광역시 군위군 내량리</t>
+  </si>
+  <si>
+    <t>경상북도 포항시남구 오천읍 항사리</t>
+  </si>
+  <si>
+    <t>경상북도 김천시 덕곡동</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 여수시 적량동</t>
+  </si>
+  <si>
+    <t>경상북도 청도군 화양읍 송북리</t>
+  </si>
+  <si>
+    <t>대구광역시 서구 중리동</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 순천시 황전면 괴목리</t>
+  </si>
+  <si>
+    <t>경상북도 경주시 외동읍 입실리</t>
+  </si>
+  <si>
+    <t>대전광역시 서구 정림동</t>
+  </si>
+  <si>
+    <t>경상북도 경산시 하양읍 금락리</t>
+  </si>
+  <si>
+    <t>대구광역시 군위군 위성리</t>
+  </si>
+  <si>
+    <t>대전광역시 유성구 구성동</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 곡성군 석곡면 유정리</t>
+  </si>
+  <si>
+    <t>경상북도 경산시 중방동</t>
+  </si>
+  <si>
+    <t>대구광역시 동구 신암동</t>
+  </si>
+  <si>
+    <t>대구광역시 동구 효목동</t>
+  </si>
+  <si>
+    <t>경상북도 구미시 남통동</t>
+  </si>
+  <si>
+    <t>경상북도 포항시북구 기계면 현내리</t>
+  </si>
+  <si>
+    <t>경상북도 포항시남구 구룡포읍 병포리</t>
+  </si>
+  <si>
+    <t>경상북도 고령군 대가야읍 내곡리</t>
+  </si>
+  <si>
+    <t>경상북도 구미시 선산읍 이문리</t>
+  </si>
+  <si>
+    <t>경상북도 경주시 탑동</t>
+  </si>
+  <si>
+    <t>경상북도 성주군 성주읍 삼산리</t>
+  </si>
+  <si>
+    <t>대구광역시 달성군 하빈면 현내리</t>
+  </si>
+  <si>
+    <t>경상북도 경주시 황성동</t>
+  </si>
+  <si>
+    <t>대구광역시 북구 서변동</t>
+  </si>
+  <si>
+    <t>경상북도 칠곡군 약목면 동안리</t>
+  </si>
+  <si>
+    <t>대구광역시 달성군 옥포읍 신당리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 구례군 마산면 사도리</t>
+  </si>
+  <si>
+    <t>대구광역시 달성군 현풍읍 원교리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 여수시 화양면 안포리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 여수시 돌산읍 서덕리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 광양시 광양읍 칠성리</t>
+  </si>
+  <si>
+    <t>경상북도 포항시 남구 호미곶면 대보리</t>
+  </si>
+  <si>
+    <t>경상북도 경주시 감포읍 나정리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 순천시 해룡면 대안리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 고흥군 포두면 송산리</t>
+  </si>
+  <si>
+    <t>경상북도 포항시남구 송도동</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 여수시 남면 연도리</t>
+  </si>
+  <si>
+    <t>전남광주통합특별시 보성군 벌교읍 장양리</t>
   </si>
 </sst>
 </file>
@@ -5286,7 +5501,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5436,15 +5651,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7445,15 +7651,18 @@
   <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="B1" s="37" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>241</v>
       </c>
       <c r="D1" s="38" t="s">
         <v>23</v>
@@ -7465,15 +7674,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="B2" s="47">
+    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="47">
         <v>133</v>
       </c>
+      <c r="B2" s="41" t="s">
+        <v>164</v>
+      </c>
       <c r="C2" s="41" t="s">
-        <v>164</v>
+        <v>290</v>
       </c>
       <c r="D2" s="41">
         <v>36.371989999999997</v>
@@ -7485,13 +7694,15 @@
         <v>67.790000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="51"/>
-      <c r="B3" s="48">
+    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="48">
         <v>648</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="B3" s="43" t="s">
         <v>165</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>274</v>
       </c>
       <c r="D3" s="43">
         <v>36.413469999999997</v>
@@ -7503,13 +7714,15 @@
         <v>99.9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
-      <c r="B4" s="48">
+    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="48">
         <v>643</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="B4" s="43" t="s">
         <v>166</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>277</v>
       </c>
       <c r="D4" s="43">
         <v>36.34019</v>
@@ -7521,13 +7734,15 @@
         <v>91.34</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="51"/>
-      <c r="B5" s="48">
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="48">
         <v>378</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="B5" s="43" t="s">
         <v>167</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>287</v>
       </c>
       <c r="D5" s="43">
         <v>36.303609999999999</v>
@@ -7539,13 +7754,15 @@
         <v>71.19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="51"/>
-      <c r="B6" s="48">
+    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="48">
         <v>642</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="B6" s="43" t="s">
         <v>168</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>261</v>
       </c>
       <c r="D6" s="43">
         <v>36.291289999999996</v>
@@ -7557,13 +7774,15 @@
         <v>148.61000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="51"/>
-      <c r="B7" s="48">
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="48">
         <v>238</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="B7" s="43" t="s">
         <v>169</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>259</v>
       </c>
       <c r="D7" s="43">
         <v>36.105629999999998</v>
@@ -7575,15 +7794,15 @@
         <v>170.17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="48">
+    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="48">
         <v>449</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>172</v>
+      <c r="B8" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>269</v>
       </c>
       <c r="D8" s="43">
         <v>37.510019999999997</v>
@@ -7595,13 +7814,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
-      <c r="B9" s="48">
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="48">
         <v>626</v>
       </c>
-      <c r="C9" s="43" t="s">
-        <v>173</v>
+      <c r="B9" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>267</v>
       </c>
       <c r="D9" s="43">
         <v>36.352939999999997</v>
@@ -7613,13 +7834,15 @@
         <v>120.57</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="51"/>
-      <c r="B10" s="48">
+    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="48">
         <v>135</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>174</v>
+      <c r="B10" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>255</v>
       </c>
       <c r="D10" s="43">
         <v>36.22025</v>
@@ -7631,13 +7854,15 @@
         <v>244.98</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="51"/>
-      <c r="B11" s="48">
+    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="48">
         <v>605</v>
       </c>
-      <c r="C11" s="43" t="s">
-        <v>175</v>
+      <c r="B11" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>262</v>
       </c>
       <c r="D11" s="43">
         <v>36.159999999999997</v>
@@ -7649,13 +7874,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="51"/>
-      <c r="B12" s="48">
+    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="48">
         <v>647</v>
       </c>
-      <c r="C12" s="43" t="s">
-        <v>176</v>
+      <c r="B12" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>268</v>
       </c>
       <c r="D12" s="43">
         <v>36.124740000000003</v>
@@ -7667,15 +7894,15 @@
         <v>118.4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13" s="48">
+    <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="48">
         <v>821</v>
       </c>
-      <c r="C13" s="43" t="s">
-        <v>178</v>
+      <c r="B13" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>276</v>
       </c>
       <c r="D13" s="43">
         <v>36.281869999999998</v>
@@ -7687,13 +7914,15 @@
         <v>91.11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="51"/>
-      <c r="B14" s="48">
+    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="48">
         <v>806</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>179</v>
+      <c r="B14" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>299</v>
       </c>
       <c r="D14" s="43">
         <v>36.233359999999998</v>
@@ -7705,13 +7934,15 @@
         <v>41.05</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="51"/>
-      <c r="B15" s="48">
+    <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="48">
         <v>847</v>
       </c>
-      <c r="C15" s="43" t="s">
-        <v>180</v>
+      <c r="B15" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>289</v>
       </c>
       <c r="D15" s="43">
         <v>36.276229999999998</v>
@@ -7723,13 +7954,15 @@
         <v>70.41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="51"/>
-      <c r="B16" s="48">
+    <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="48">
         <v>823</v>
       </c>
-      <c r="C16" s="43" t="s">
-        <v>181</v>
+      <c r="B16" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>279</v>
       </c>
       <c r="D16" s="43">
         <v>36.249339999999997</v>
@@ -7741,13 +7974,15 @@
         <v>81.56</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
-      <c r="B17" s="48">
+    <row r="17" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="48">
         <v>807</v>
       </c>
-      <c r="C17" s="43" t="s">
-        <v>182</v>
+      <c r="B17" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>271</v>
       </c>
       <c r="D17" s="43">
         <v>36.179659999999998</v>
@@ -7759,13 +7994,15 @@
         <v>114.26</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="51"/>
-      <c r="B18" s="48">
+    <row r="18" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="48">
         <v>841</v>
       </c>
-      <c r="C18" s="43" t="s">
-        <v>183</v>
+      <c r="B18" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>263</v>
       </c>
       <c r="D18" s="43">
         <v>36.084940000000003</v>
@@ -7777,13 +8014,15 @@
         <v>138.88</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
-      <c r="B19" s="48">
+    <row r="19" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="48">
         <v>830</v>
       </c>
-      <c r="C19" s="43" t="s">
-        <v>184</v>
+      <c r="B19" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>296</v>
       </c>
       <c r="D19" s="43">
         <v>36.068869999999997</v>
@@ -7795,13 +8034,15 @@
         <v>45.06</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="51"/>
-      <c r="B20" s="48">
+    <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="48">
         <v>138</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>185</v>
+      <c r="B20" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>316</v>
       </c>
       <c r="D20" s="43">
         <v>36.03201</v>
@@ -7813,13 +8054,15 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="51"/>
-      <c r="B21" s="48">
+    <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="48">
         <v>808</v>
       </c>
-      <c r="C21" s="43" t="s">
-        <v>186</v>
+      <c r="B21" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>312</v>
       </c>
       <c r="D21" s="43">
         <v>36.075969999999998</v>
@@ -7831,13 +8074,15 @@
         <v>11.41</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
-      <c r="B22" s="48">
+    <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="48">
         <v>816</v>
       </c>
-      <c r="C22" s="43" t="s">
-        <v>187</v>
+      <c r="B22" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>297</v>
       </c>
       <c r="D22" s="43">
         <v>35.9831</v>
@@ -7849,13 +8094,15 @@
         <v>42.37</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="51"/>
-      <c r="B23" s="48">
+    <row r="23" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="48">
         <v>995</v>
       </c>
-      <c r="C23" s="43" t="s">
-        <v>188</v>
+      <c r="B23" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>280</v>
       </c>
       <c r="D23" s="43">
         <v>35.928600000000003</v>
@@ -7867,13 +8114,15 @@
         <v>80.319999999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="51"/>
-      <c r="B24" s="48">
+    <row r="24" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="48">
         <v>850</v>
       </c>
-      <c r="C24" s="43" t="s">
-        <v>189</v>
+      <c r="B24" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>313</v>
       </c>
       <c r="D24" s="43">
         <v>35.784709999999997</v>
@@ -7885,13 +8134,15 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
-      <c r="B25" s="48">
+    <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="48">
         <v>859</v>
       </c>
-      <c r="C25" s="43" t="s">
-        <v>190</v>
+      <c r="B25" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>248</v>
       </c>
       <c r="D25" s="43">
         <v>35.754899999999999</v>
@@ -7903,13 +8154,15 @@
         <v>475</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="51"/>
-      <c r="B26" s="48">
+    <row r="26" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="48">
         <v>829</v>
       </c>
-      <c r="C26" s="43" t="s">
-        <v>191</v>
+      <c r="B26" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>286</v>
       </c>
       <c r="D26" s="43">
         <v>35.712139999999998</v>
@@ -7921,13 +8174,15 @@
         <v>72.92</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="51"/>
-      <c r="B27" s="48">
+    <row r="27" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="48">
         <v>811</v>
       </c>
-      <c r="C27" s="43" t="s">
-        <v>192</v>
+      <c r="B27" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>303</v>
       </c>
       <c r="D27" s="43">
         <v>35.862990000000003</v>
@@ -7939,13 +8194,15 @@
         <v>32.36</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="51"/>
-      <c r="B28" s="48">
+    <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="48">
         <v>283</v>
       </c>
-      <c r="C28" s="43" t="s">
-        <v>193</v>
+      <c r="B28" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>300</v>
       </c>
       <c r="D28" s="43">
         <v>35.81747</v>
@@ -7957,13 +8214,15 @@
         <v>40.130000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="51"/>
-      <c r="B29" s="48">
+    <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="48">
         <v>842</v>
       </c>
-      <c r="C29" s="43" t="s">
-        <v>194</v>
+      <c r="B29" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>258</v>
       </c>
       <c r="D29" s="43">
         <v>35.757599999999996</v>
@@ -7975,13 +8234,15 @@
         <v>170.66</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="51"/>
-      <c r="B30" s="48">
+    <row r="30" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="48">
         <v>826</v>
       </c>
-      <c r="C30" s="43" t="s">
-        <v>195</v>
+      <c r="B30" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>266</v>
       </c>
       <c r="D30" s="43">
         <v>36.047089999999997</v>
@@ -7993,13 +8254,15 @@
         <v>130.97999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="51"/>
-      <c r="B31" s="48">
+    <row r="31" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="48">
         <v>281</v>
       </c>
-      <c r="C31" s="43" t="s">
-        <v>196</v>
+      <c r="B31" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>275</v>
       </c>
       <c r="D31" s="43">
         <v>35.977420000000002</v>
@@ -8011,13 +8274,15 @@
         <v>96.12</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="51"/>
-      <c r="B32" s="48">
+    <row r="32" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="48">
         <v>840</v>
       </c>
-      <c r="C32" s="43" t="s">
-        <v>197</v>
+      <c r="B32" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>288</v>
       </c>
       <c r="D32" s="43">
         <v>35.912599999999998</v>
@@ -8029,13 +8294,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="51"/>
-      <c r="B33" s="48">
+    <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="48">
         <v>827</v>
       </c>
-      <c r="C33" s="43" t="s">
-        <v>198</v>
+      <c r="B33" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>292</v>
       </c>
       <c r="D33" s="43">
         <v>35.824249999999999</v>
@@ -8047,13 +8314,15 @@
         <v>61.21</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="51"/>
-      <c r="B34" s="48">
+    <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="48">
         <v>848</v>
       </c>
-      <c r="C34" s="43" t="s">
-        <v>199</v>
+      <c r="B34" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>272</v>
       </c>
       <c r="D34" s="43">
         <v>35.679160000000003</v>
@@ -8065,13 +8334,15 @@
         <v>104.4</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="51"/>
-      <c r="B35" s="48">
+    <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="48">
         <v>813</v>
       </c>
-      <c r="C35" s="43" t="s">
-        <v>200</v>
+      <c r="B35" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>283</v>
       </c>
       <c r="D35" s="43">
         <v>35.654040000000002</v>
@@ -8083,13 +8354,15 @@
         <v>77.53</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="51"/>
-      <c r="B36" s="48">
+    <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="48">
         <v>143</v>
       </c>
-      <c r="C36" s="43" t="s">
-        <v>201</v>
+      <c r="B36" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>294</v>
       </c>
       <c r="D36" s="43">
         <v>35.877969999999998</v>
@@ -8101,13 +8374,15 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="51"/>
-      <c r="B37" s="48">
+    <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="48">
         <v>860</v>
       </c>
-      <c r="C37" s="43" t="s">
-        <v>202</v>
+      <c r="B37" s="43" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>293</v>
       </c>
       <c r="D37" s="43">
         <v>35.885150000000003</v>
@@ -8119,13 +8394,15 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="51"/>
-      <c r="B38" s="48">
+    <row r="38" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="48">
         <v>845</v>
       </c>
-      <c r="C38" s="43" t="s">
-        <v>203</v>
+      <c r="B38" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>304</v>
       </c>
       <c r="D38" s="43">
         <v>35.90842</v>
@@ -8137,13 +8414,15 @@
         <v>30.18</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="51"/>
-      <c r="B39" s="48">
+    <row r="39" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="48">
         <v>846</v>
       </c>
-      <c r="C39" s="43" t="s">
-        <v>204</v>
+      <c r="B39" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>284</v>
       </c>
       <c r="D39" s="43">
         <v>35.865090000000002</v>
@@ -8155,13 +8434,15 @@
         <v>76.37</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="51"/>
-      <c r="B40" s="48">
+    <row r="40" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="48">
         <v>991</v>
       </c>
-      <c r="C40" s="43" t="s">
-        <v>205</v>
+      <c r="B40" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>306</v>
       </c>
       <c r="D40" s="43">
         <v>35.802790000000002</v>
@@ -8173,13 +8454,15 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="51"/>
-      <c r="B41" s="48">
+    <row r="41" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="48">
         <v>828</v>
       </c>
-      <c r="C41" s="43" t="s">
-        <v>206</v>
+      <c r="B41" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>308</v>
       </c>
       <c r="D41" s="43">
         <v>35.690179999999998</v>
@@ -8191,13 +8474,15 @@
         <v>24.93</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="51"/>
-      <c r="B42" s="48">
+    <row r="42" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="48">
         <v>992</v>
       </c>
-      <c r="C42" s="43" t="s">
-        <v>207</v>
+      <c r="B42" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>302</v>
       </c>
       <c r="D42" s="43">
         <v>35.906199999999998</v>
@@ -8209,13 +8494,15 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="51"/>
-      <c r="B43" s="48">
+    <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="48">
         <v>853</v>
       </c>
-      <c r="C43" s="43" t="s">
-        <v>208</v>
+      <c r="B43" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>245</v>
       </c>
       <c r="D43" s="43">
         <v>36.018270000000001</v>
@@ -8227,13 +8514,15 @@
         <v>568.37</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="51"/>
-      <c r="B44" s="48">
+    <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="48">
         <v>824</v>
       </c>
-      <c r="C44" s="43" t="s">
-        <v>209</v>
+      <c r="B44" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>270</v>
       </c>
       <c r="D44" s="43">
         <v>36.095599999999997</v>
@@ -8245,13 +8534,15 @@
         <v>114.95</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="51"/>
-      <c r="B45" s="48">
+    <row r="45" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="48">
         <v>825</v>
       </c>
-      <c r="C45" s="43" t="s">
-        <v>210</v>
+      <c r="B45" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>305</v>
       </c>
       <c r="D45" s="43">
         <v>36.039769999999997</v>
@@ -8263,13 +8554,15 @@
         <v>29.79</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="51"/>
-      <c r="B46" s="48">
+    <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="48">
         <v>279</v>
       </c>
-      <c r="C46" s="43" t="s">
-        <v>211</v>
+      <c r="B46" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>295</v>
       </c>
       <c r="D46" s="43">
         <v>36.130549999999999</v>
@@ -8281,13 +8574,15 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="51"/>
-      <c r="B47" s="48">
+    <row r="47" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="48">
         <v>828</v>
       </c>
-      <c r="C47" s="43" t="s">
-        <v>206</v>
+      <c r="B47" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>308</v>
       </c>
       <c r="D47" s="43">
         <v>35.690179999999998</v>
@@ -8299,13 +8594,15 @@
         <v>24.93</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="51"/>
-      <c r="B48" s="48">
+    <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="48">
         <v>812</v>
       </c>
-      <c r="C48" s="43" t="s">
-        <v>212</v>
+      <c r="B48" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>298</v>
       </c>
       <c r="D48" s="43">
         <v>35.69603</v>
@@ -8317,13 +8614,15 @@
         <v>41.19</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="51"/>
-      <c r="B49" s="48">
+    <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="48">
         <v>810</v>
       </c>
-      <c r="C49" s="43" t="s">
-        <v>213</v>
+      <c r="B49" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>301</v>
       </c>
       <c r="D49" s="43">
         <v>35.925519999999999</v>
@@ -8335,13 +8634,15 @@
         <v>39.43</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="51"/>
-      <c r="B50" s="48">
+    <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="48">
         <v>809</v>
       </c>
-      <c r="C50" s="43" t="s">
-        <v>214</v>
+      <c r="B50" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>257</v>
       </c>
       <c r="D50" s="43">
         <v>35.93544</v>
@@ -8353,13 +8654,15 @@
         <v>205.1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="51"/>
-      <c r="B51" s="48">
+    <row r="51" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="48">
         <v>822</v>
       </c>
-      <c r="C51" s="43" t="s">
-        <v>215</v>
+      <c r="B51" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>281</v>
       </c>
       <c r="D51" s="43">
         <v>36.119869999999999</v>
@@ -8371,15 +8674,15 @@
         <v>79.239999999999995</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="B52" s="48">
+    <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="48">
         <v>701</v>
       </c>
-      <c r="C52" s="43" t="s">
-        <v>217</v>
+      <c r="B52" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="C52" s="41" t="s">
+        <v>256</v>
       </c>
       <c r="D52" s="43">
         <v>36.00168</v>
@@ -8391,13 +8694,15 @@
         <v>212</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="51"/>
-      <c r="B53" s="48">
+    <row r="53" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="48">
         <v>735</v>
       </c>
-      <c r="C53" s="43" t="s">
-        <v>218</v>
+      <c r="B53" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="41" t="s">
+        <v>244</v>
       </c>
       <c r="D53" s="43">
         <v>35.894240000000003</v>
@@ -8409,13 +8714,15 @@
         <v>660.36</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="51"/>
-      <c r="B54" s="48">
+    <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="48">
         <v>314</v>
       </c>
-      <c r="C54" s="43" t="s">
-        <v>219</v>
+      <c r="B54" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" s="41" t="s">
+        <v>242</v>
       </c>
       <c r="D54" s="43">
         <v>35.866210000000002</v>
@@ -8427,13 +8734,15 @@
         <v>1515.31</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="51"/>
-      <c r="B55" s="48">
+    <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="48">
         <v>757</v>
       </c>
-      <c r="C55" s="43" t="s">
-        <v>220</v>
+      <c r="B55" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" s="41" t="s">
+        <v>254</v>
       </c>
       <c r="D55" s="43">
         <v>35.974359999999997</v>
@@ -8445,13 +8754,15 @@
         <v>269.51</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="51"/>
-      <c r="B56" s="48">
+    <row r="56" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="48">
         <v>758</v>
       </c>
-      <c r="C56" s="43" t="s">
-        <v>221</v>
+      <c r="B56" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="C56" s="41" t="s">
+        <v>252</v>
       </c>
       <c r="D56" s="43">
         <v>35.835209999999996</v>
@@ -8463,13 +8774,15 @@
         <v>320.61</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="51"/>
-      <c r="B57" s="48">
+    <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="48">
         <v>703</v>
       </c>
-      <c r="C57" s="43" t="s">
-        <v>222</v>
+      <c r="B57" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>251</v>
       </c>
       <c r="D57" s="43">
         <v>35.760359999999999</v>
@@ -8481,13 +8794,15 @@
         <v>354.27</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="51"/>
-      <c r="B58" s="48">
+    <row r="58" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="48">
         <v>248</v>
       </c>
-      <c r="C58" s="43" t="s">
-        <v>223</v>
+      <c r="B58" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="41" t="s">
+        <v>250</v>
       </c>
       <c r="D58" s="43">
         <v>35.656959999999998</v>
@@ -8499,13 +8814,15 @@
         <v>406.87</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="51"/>
-      <c r="B59" s="48">
+    <row r="59" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="48">
         <v>379</v>
       </c>
-      <c r="C59" s="43" t="s">
-        <v>224</v>
+      <c r="B59" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="C59" s="41" t="s">
+        <v>253</v>
       </c>
       <c r="D59" s="43">
         <v>35.540460000000003</v>
@@ -8517,13 +8834,15 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="51"/>
-      <c r="B60" s="48">
+    <row r="60" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="48">
         <v>247</v>
       </c>
-      <c r="C60" s="43" t="s">
-        <v>225</v>
+      <c r="B60" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" s="41" t="s">
+        <v>265</v>
       </c>
       <c r="D60" s="43">
         <v>35.421300000000002</v>
@@ -8535,13 +8854,15 @@
         <v>133.49</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="51"/>
-      <c r="B61" s="48">
+    <row r="61" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="48">
         <v>759</v>
       </c>
-      <c r="C61" s="43" t="s">
-        <v>226</v>
+      <c r="B61" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="41" t="s">
+        <v>247</v>
       </c>
       <c r="D61" s="43">
         <v>35.37162</v>
@@ -8553,15 +8874,15 @@
         <v>478.65</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="51" t="s">
-        <v>227</v>
-      </c>
-      <c r="B62" s="48">
+    <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="48">
         <v>315</v>
       </c>
-      <c r="C62" s="43" t="s">
-        <v>228</v>
+      <c r="B62" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="C62" s="41" t="s">
+        <v>243</v>
       </c>
       <c r="D62" s="43">
         <v>35.306730000000002</v>
@@ -8573,13 +8894,15 @@
         <v>1087.8599999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="51"/>
-      <c r="B63" s="48">
+    <row r="63" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="48">
         <v>791</v>
       </c>
-      <c r="C63" s="43" t="s">
-        <v>229</v>
+      <c r="B63" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63" s="41" t="s">
+        <v>249</v>
       </c>
       <c r="D63" s="43">
         <v>35.266210000000001</v>
@@ -8591,13 +8914,15 @@
         <v>410.15</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="51"/>
-      <c r="B64" s="48">
+    <row r="64" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="48">
         <v>709</v>
       </c>
-      <c r="C64" s="43" t="s">
-        <v>230</v>
+      <c r="B64" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="C64" s="41" t="s">
+        <v>307</v>
       </c>
       <c r="D64" s="43">
         <v>35.208080000000002</v>
@@ -8609,13 +8934,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="51"/>
-      <c r="B65" s="48">
+    <row r="65" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="48">
         <v>856</v>
       </c>
-      <c r="C65" s="43" t="s">
-        <v>231</v>
+      <c r="B65" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="C65" s="41" t="s">
+        <v>246</v>
       </c>
       <c r="D65" s="43">
         <v>35.101799999999997</v>
@@ -8627,13 +8954,15 @@
         <v>514.84</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="51"/>
-      <c r="B66" s="48">
+    <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="48">
         <v>266</v>
       </c>
-      <c r="C66" s="43" t="s">
-        <v>232</v>
+      <c r="B66" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="C66" s="41" t="s">
+        <v>278</v>
       </c>
       <c r="D66" s="43">
         <v>34.943399999999997</v>
@@ -8645,13 +8974,15 @@
         <v>88.21</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="51"/>
-      <c r="B67" s="48">
+    <row r="67" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="48">
         <v>713</v>
       </c>
-      <c r="C67" s="43" t="s">
-        <v>233</v>
+      <c r="B67" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="C67" s="41" t="s">
+        <v>311</v>
       </c>
       <c r="D67" s="43">
         <v>34.975070000000002</v>
@@ -8663,13 +8994,15 @@
         <v>15.56</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="51"/>
-      <c r="B68" s="48">
+    <row r="68" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="48">
         <v>766</v>
       </c>
-      <c r="C68" s="43" t="s">
-        <v>234</v>
+      <c r="B68" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="C68" s="41" t="s">
+        <v>282</v>
       </c>
       <c r="D68" s="43">
         <v>34.849460000000001</v>
@@ -8681,13 +9014,15 @@
         <v>78.86</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="51"/>
-      <c r="B69" s="48">
+    <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="48">
         <v>766</v>
       </c>
-      <c r="C69" s="43" t="s">
-        <v>234</v>
+      <c r="B69" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="C69" s="41" t="s">
+        <v>282</v>
       </c>
       <c r="D69" s="43">
         <v>34.849460000000001</v>
@@ -8699,13 +9034,15 @@
         <v>78.86</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="51"/>
-      <c r="B70" s="48">
+    <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="48">
         <v>786</v>
       </c>
-      <c r="C70" s="43" t="s">
-        <v>235</v>
+      <c r="B70" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C70" s="41" t="s">
+        <v>310</v>
       </c>
       <c r="D70" s="43">
         <v>34.638109999999998</v>
@@ -8717,13 +9054,15 @@
         <v>20.27</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="51"/>
-      <c r="B71" s="48">
+    <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="48">
         <v>750</v>
       </c>
-      <c r="C71" s="43" t="s">
-        <v>236</v>
+      <c r="B71" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="C71" s="41" t="s">
+        <v>309</v>
       </c>
       <c r="D71" s="43">
         <v>34.627809999999997</v>
@@ -8735,13 +9074,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="51"/>
-      <c r="B72" s="48">
+    <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="48">
         <v>306</v>
       </c>
-      <c r="C72" s="43" t="s">
-        <v>237</v>
+      <c r="B72" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="C72" s="41" t="s">
+        <v>317</v>
       </c>
       <c r="D72" s="43">
         <v>34.431849999999997</v>
@@ -8753,13 +9094,15 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="51"/>
-      <c r="B73" s="48">
+    <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="48">
         <v>790</v>
       </c>
-      <c r="C73" s="43" t="s">
-        <v>238</v>
+      <c r="B73" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="C73" s="41" t="s">
+        <v>264</v>
       </c>
       <c r="D73" s="43">
         <v>34.532580000000003</v>
@@ -8771,13 +9114,15 @@
         <v>135.19</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="51"/>
-      <c r="B74" s="48">
+    <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="48">
         <v>767</v>
       </c>
-      <c r="C74" s="43" t="s">
-        <v>239</v>
+      <c r="B74" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" s="41" t="s">
+        <v>315</v>
       </c>
       <c r="D74" s="43">
         <v>34.588529999999999</v>
@@ -8789,13 +9134,15 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="51"/>
-      <c r="B75" s="48">
+    <row r="75" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="48">
         <v>748</v>
       </c>
-      <c r="C75" s="43" t="s">
-        <v>240</v>
+      <c r="B75" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C75" s="41" t="s">
+        <v>318</v>
       </c>
       <c r="D75" s="43">
         <v>34.836939999999998</v>
@@ -8807,13 +9154,15 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="51"/>
-      <c r="B76" s="48">
+    <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="48">
         <v>174</v>
       </c>
-      <c r="C76" s="43" t="s">
-        <v>241</v>
+      <c r="B76" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="C76" s="41" t="s">
+        <v>260</v>
       </c>
       <c r="D76" s="43">
         <v>35.020400000000002</v>
@@ -8825,13 +9174,15 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="51"/>
-      <c r="B77" s="48">
+    <row r="77" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="48">
         <v>712</v>
       </c>
-      <c r="C77" s="43" t="s">
-        <v>242</v>
+      <c r="B77" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="C77" s="41" t="s">
+        <v>314</v>
       </c>
       <c r="D77" s="43">
         <v>34.903509999999997</v>
@@ -8843,13 +9194,15 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="51"/>
-      <c r="B78" s="48">
+    <row r="78" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="48">
         <v>794</v>
       </c>
-      <c r="C78" s="43" t="s">
-        <v>243</v>
+      <c r="B78" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="C78" s="41" t="s">
+        <v>285</v>
       </c>
       <c r="D78" s="43">
         <v>35.100659999999998</v>
@@ -8861,13 +9214,15 @@
         <v>75.989999999999995</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="51"/>
-      <c r="B79" s="48">
+    <row r="79" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="48">
         <v>687</v>
       </c>
-      <c r="C79" s="43" t="s">
-        <v>244</v>
+      <c r="B79" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="C79" s="41" t="s">
+        <v>291</v>
       </c>
       <c r="D79" s="43">
         <v>35.126190000000001</v>
@@ -8880,12 +9235,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="52"/>
-      <c r="B80" s="49">
+      <c r="A80" s="49">
         <v>768</v>
       </c>
-      <c r="C80" s="45" t="s">
-        <v>245</v>
+      <c r="B80" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="C80" s="41" t="s">
+        <v>273</v>
       </c>
       <c r="D80" s="45">
         <v>35.28886</v>
@@ -8898,13 +9255,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A51"/>
-    <mergeCell ref="A52:A61"/>
-    <mergeCell ref="A62:A80"/>
-  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ASOS, AWS 지점정보(부산관할)_수정.xlsx
+++ b/ASOS, AWS 지점정보(부산관할)_수정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92E9A9-294F-4378-9978-458543CFD7D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE5DB19-69E6-45E1-A150-D87F074D6CBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{9D2C116D-9A81-45CD-ABAE-F1BEFBD84F46}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="3" xr2:uid="{9D2C116D-9A81-45CD-ABAE-F1BEFBD84F46}"/>
   </bookViews>
   <sheets>
     <sheet name="ASOS" sheetId="1" r:id="rId1"/>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="48">
-        <v>449</v>
+        <v>604</v>
       </c>
       <c r="B8" s="43" t="s">
         <v>170</v>
@@ -7805,13 +7805,13 @@
         <v>269</v>
       </c>
       <c r="D8" s="43">
-        <v>37.510019999999997</v>
+        <v>36.299950000000003</v>
       </c>
       <c r="E8" s="43">
-        <v>127.44808999999999</v>
+        <v>127.59654</v>
       </c>
       <c r="F8" s="44">
-        <v>32</v>
+        <v>118.05</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
